--- a/data/jewelry.xlsx
+++ b/data/jewelry.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:L3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -405,19 +405,12 @@
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="50.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
-    <col min="15" max="15" width="10.83203125" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="17" width="10.83203125" customWidth="1"/>
-    <col min="18" max="18" width="10.83203125" customWidth="1"/>
-    <col min="19" max="19" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -440,43 +433,22 @@
         <v>currentPrice</v>
       </c>
       <c r="G1" t="str">
-        <v>change24h</v>
+        <v>notes</v>
       </c>
       <c r="H1" t="str">
-        <v>notes</v>
+        <v>accountType</v>
       </c>
       <c r="I1" t="str">
-        <v>accountType</v>
+        <v>accountName</v>
       </c>
       <c r="J1" t="str">
-        <v>accountName</v>
+        <v>costBasis</v>
       </c>
       <c r="K1" t="str">
-        <v>costBasis</v>
+        <v>purchaseDate</v>
       </c>
       <c r="L1" t="str">
-        <v>purchaseDate</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Day 1</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Day 2</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Day 3</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Day 4</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Day 5</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Day 6</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Day 7</v>
+        <v>lastUpdated</v>
       </c>
     </row>
     <row r="2">
@@ -498,44 +470,23 @@
       <c r="F2">
         <v>16200</v>
       </c>
-      <c r="G2">
-        <v>0</v>
+      <c r="G2" t="str">
+        <v>Ref. 126610LN. Purchased 2023. Appreciating.</v>
       </c>
       <c r="H2" t="str">
-        <v>Ref. 126610LN. Purchased 2023. Appreciating.</v>
+        <v>direct</v>
       </c>
       <c r="I2" t="str">
-        <v>direct</v>
-      </c>
-      <c r="J2" t="str">
         <v>Personal Property</v>
       </c>
-      <c r="K2">
+      <c r="J2">
         <v>12800</v>
       </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
       <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2">
-        <v>16200</v>
-      </c>
-      <c r="N2">
-        <v>16200</v>
-      </c>
-      <c r="O2">
-        <v>16200</v>
-      </c>
-      <c r="P2">
-        <v>16200</v>
-      </c>
-      <c r="Q2">
-        <v>16200</v>
-      </c>
-      <c r="R2">
-        <v>16200</v>
-      </c>
-      <c r="S2">
-        <v>16200</v>
+        <v>2026-02-11</v>
       </c>
     </row>
     <row r="3">
@@ -557,49 +508,28 @@
       <c r="F3">
         <v>7200</v>
       </c>
-      <c r="G3">
-        <v>0</v>
+      <c r="G3" t="str">
+        <v>1.5ct round brilliant. Appraised value.</v>
       </c>
       <c r="H3" t="str">
-        <v>1.5ct round brilliant. Appraised value.</v>
+        <v>direct</v>
       </c>
       <c r="I3" t="str">
-        <v>direct</v>
-      </c>
-      <c r="J3" t="str">
         <v>Personal Property</v>
       </c>
-      <c r="K3">
+      <c r="J3">
         <v>8500</v>
       </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
       <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3">
-        <v>7200</v>
-      </c>
-      <c r="N3">
-        <v>7200</v>
-      </c>
-      <c r="O3">
-        <v>7200</v>
-      </c>
-      <c r="P3">
-        <v>7200</v>
-      </c>
-      <c r="Q3">
-        <v>7200</v>
-      </c>
-      <c r="R3">
-        <v>7200</v>
-      </c>
-      <c r="S3">
-        <v>7200</v>
+        <v>2026-02-11</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/jewelry.xlsx
+++ b/data/jewelry.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L1"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -451,85 +451,9 @@
         <v>lastUpdated</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>rolex-sub</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Rolex Submariner</v>
-      </c>
-      <c r="C2" t="str">
-        <v>WATCH</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>12800</v>
-      </c>
-      <c r="F2">
-        <v>16200</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Ref. 126610LN. Purchased 2023. Appreciating.</v>
-      </c>
-      <c r="H2" t="str">
-        <v>direct</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Personal Property</v>
-      </c>
-      <c r="J2">
-        <v>12800</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v>2026-02-11</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>diamond-ring</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Diamond Engagement Ring</v>
-      </c>
-      <c r="C3" t="str">
-        <v>JEWEL</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>8500</v>
-      </c>
-      <c r="F3">
-        <v>7200</v>
-      </c>
-      <c r="G3" t="str">
-        <v>1.5ct round brilliant. Appraised value.</v>
-      </c>
-      <c r="H3" t="str">
-        <v>direct</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Personal Property</v>
-      </c>
-      <c r="J3">
-        <v>8500</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>2026-02-11</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/jewelry.xlsx
+++ b/data/jewelry.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L3"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -451,9 +451,85 @@
         <v>lastUpdated</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>rolex-sub</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Rolex Submariner</v>
+      </c>
+      <c r="C2" t="str">
+        <v>WATCH</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>14000</v>
+      </c>
+      <c r="F2">
+        <v>17500</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Ref. 126610LN. Purchased 2023. Appreciating.</v>
+      </c>
+      <c r="H2" t="str">
+        <v>direct</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Personal Property</v>
+      </c>
+      <c r="J2">
+        <v>14000</v>
+      </c>
+      <c r="K2" t="str">
+        <v>2023-08-01</v>
+      </c>
+      <c r="L2" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>diamond-ring</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Diamond Engagement Ring</v>
+      </c>
+      <c r="C3" t="str">
+        <v>JEWEL</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>12000</v>
+      </c>
+      <c r="F3">
+        <v>10000</v>
+      </c>
+      <c r="G3" t="str">
+        <v>1.5ct round brilliant. Appraised value.</v>
+      </c>
+      <c r="H3" t="str">
+        <v>direct</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Personal Property</v>
+      </c>
+      <c r="J3">
+        <v>12000</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2018-12-01</v>
+      </c>
+      <c r="L3" t="str">
+        <v>2026-02-12</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/jewelry.xlsx
+++ b/data/jewelry.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L1"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -451,85 +451,9 @@
         <v>lastUpdated</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>rolex-sub</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Rolex Submariner</v>
-      </c>
-      <c r="C2" t="str">
-        <v>WATCH</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>14000</v>
-      </c>
-      <c r="F2">
-        <v>17500</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Ref. 126610LN. Purchased 2023. Appreciating.</v>
-      </c>
-      <c r="H2" t="str">
-        <v>direct</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Personal Property</v>
-      </c>
-      <c r="J2">
-        <v>14000</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2023-08-01</v>
-      </c>
-      <c r="L2" t="str">
-        <v>2026-02-12</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>diamond-ring</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Diamond Engagement Ring</v>
-      </c>
-      <c r="C3" t="str">
-        <v>JEWEL</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>12000</v>
-      </c>
-      <c r="F3">
-        <v>10000</v>
-      </c>
-      <c r="G3" t="str">
-        <v>1.5ct round brilliant. Appraised value.</v>
-      </c>
-      <c r="H3" t="str">
-        <v>direct</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Personal Property</v>
-      </c>
-      <c r="J3">
-        <v>12000</v>
-      </c>
-      <c r="K3" t="str">
-        <v>2018-12-01</v>
-      </c>
-      <c r="L3" t="str">
-        <v>2026-02-12</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L1"/>
   </ignoredErrors>
 </worksheet>
 </file>